--- a/TestData/TestingExcel.xlsx
+++ b/TestData/TestingExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d285987eec67a25b/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{CB318F6B-CA34-476C-BC71-88630351260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2916BC8F-CD02-4A71-A793-87B35894A073}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{CB318F6B-CA34-476C-BC71-88630351260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25A2A8E0-AD9D-48C3-BA3B-9A5E97FB539D}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="16956" windowHeight="8880" activeTab="1" xr2:uid="{A38E351B-4DC6-46A3-9E97-7B192F9FEE00}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="16956" windowHeight="8880" xr2:uid="{A38E351B-4DC6-46A3-9E97-7B192F9FEE00}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <t>Email</t>
   </si>
@@ -65,12 +65,6 @@
     <t>Test@456</t>
   </si>
   <si>
-    <t>kumaran.test03@example.com</t>
-  </si>
-  <si>
-    <t>Test@789</t>
-  </si>
-  <si>
     <t>arun.test04@example.com</t>
   </si>
   <si>
@@ -89,24 +83,12 @@
     <t>Test@303</t>
   </si>
   <si>
-    <t>rahul.test07@example.com</t>
-  </si>
-  <si>
-    <t>Test@404</t>
-  </si>
-  <si>
     <t>divya.test08@example.com</t>
   </si>
   <si>
     <t>Test@505</t>
   </si>
   <si>
-    <t>karthik.test09@example.com</t>
-  </si>
-  <si>
-    <t>Test@606</t>
-  </si>
-  <si>
     <t>anitha.test10@example.com</t>
   </si>
   <si>
@@ -210,6 +192,15 @@
   </si>
   <si>
     <t>Sankar1234</t>
+  </si>
+  <si>
+    <t>staus</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -602,115 +593,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{798466B8-8672-4CB5-9182-87D652BA1622}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.77734375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>123456</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>123456</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>23</v>
+      <c r="C13" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -719,15 +749,14 @@
     <hyperlink ref="A3" r:id="rId2" xr:uid="{33E3A2C8-4C8C-4457-871B-4394B17F6D75}"/>
     <hyperlink ref="A4" r:id="rId3" display="mailto:sivakumar.test01@example.com" xr:uid="{4A1684AD-8B3F-4B9A-A920-97F8BA4A29AB}"/>
     <hyperlink ref="A5" r:id="rId4" display="mailto:santhosh.test02@example.com" xr:uid="{511B95F0-F096-4225-B499-0AC9C8932CAB}"/>
-    <hyperlink ref="A6" r:id="rId5" display="mailto:kumaran.test03@example.com" xr:uid="{8EE58DF5-196D-4A61-A35F-A9D283CBBD51}"/>
-    <hyperlink ref="A7" r:id="rId6" display="mailto:arun.test04@example.com" xr:uid="{41A92B1A-A489-482C-8820-4873106ED8CB}"/>
-    <hyperlink ref="A8" r:id="rId7" display="mailto:priya.test05@example.com" xr:uid="{A76D7F7B-7589-4A88-9F71-90C697A63E13}"/>
-    <hyperlink ref="A9" r:id="rId8" display="mailto:kavya.test06@example.com" xr:uid="{66B8BDA5-BF58-4A11-82CC-B192E2B3B1D1}"/>
-    <hyperlink ref="A10" r:id="rId9" display="mailto:rahul.test07@example.com" xr:uid="{D5A51A6F-F192-4CA0-B0AE-6BC0655D4F12}"/>
-    <hyperlink ref="A11" r:id="rId10" display="mailto:divya.test08@example.com" xr:uid="{AB5B4D43-AA83-4108-842B-FC1AD0CCA9B2}"/>
-    <hyperlink ref="A12" r:id="rId11" display="mailto:karthik.test09@example.com" xr:uid="{BB074988-4997-4ECA-A5C6-74295B6D0119}"/>
-    <hyperlink ref="A13" r:id="rId12" display="mailto:anitha.test10@example.com" xr:uid="{B872C053-BF0C-469D-ABFA-54EB2CC58BA5}"/>
-    <hyperlink ref="B13" r:id="rId13" xr:uid="{6C176E42-7FF6-4D39-A335-F43E9A74359C}"/>
+    <hyperlink ref="A7" r:id="rId5" display="mailto:arun.test04@example.com" xr:uid="{41A92B1A-A489-482C-8820-4873106ED8CB}"/>
+    <hyperlink ref="A8" r:id="rId6" display="mailto:priya.test05@example.com" xr:uid="{A76D7F7B-7589-4A88-9F71-90C697A63E13}"/>
+    <hyperlink ref="A9" r:id="rId7" display="mailto:kavya.test06@example.com" xr:uid="{66B8BDA5-BF58-4A11-82CC-B192E2B3B1D1}"/>
+    <hyperlink ref="A11" r:id="rId8" display="mailto:divya.test08@example.com" xr:uid="{AB5B4D43-AA83-4108-842B-FC1AD0CCA9B2}"/>
+    <hyperlink ref="A13" r:id="rId9" display="mailto:anitha.test10@example.com" xr:uid="{B872C053-BF0C-469D-ABFA-54EB2CC58BA5}"/>
+    <hyperlink ref="B13" r:id="rId10" xr:uid="{6C176E42-7FF6-4D39-A335-F43E9A74359C}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{2CF102D4-D426-43B2-B966-8FC7CC86D883}"/>
+    <hyperlink ref="B12" r:id="rId12" xr:uid="{01A16E32-5A28-423A-97BD-06559A8EC059}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -746,7 +775,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -755,113 +784,113 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -894,28 +923,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TestingExcel.xlsx
+++ b/TestData/TestingExcel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d285987eec67a25b/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{CB318F6B-CA34-476C-BC71-88630351260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25A2A8E0-AD9D-48C3-BA3B-9A5E97FB539D}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{CB318F6B-CA34-476C-BC71-88630351260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADCE9DDA-0DBA-4982-B288-B7E9FD592057}"/>
   <bookViews>
     <workbookView xWindow="1428" yWindow="1428" windowWidth="16956" windowHeight="8880" xr2:uid="{A38E351B-4DC6-46A3-9E97-7B192F9FEE00}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>Email</t>
   </si>
@@ -50,33 +50,18 @@
     <t>sivakumarirulaye@gmail.com</t>
   </si>
   <si>
-    <t>santhosh@gmail.com</t>
-  </si>
-  <si>
     <t>sivakumar.test01@example.com</t>
   </si>
   <si>
     <t>Test@123</t>
   </si>
   <si>
-    <t>santhosh.test02@example.com</t>
-  </si>
-  <si>
-    <t>Test@456</t>
-  </si>
-  <si>
     <t>arun.test04@example.com</t>
   </si>
   <si>
     <t>Test@101</t>
   </si>
   <si>
-    <t>priya.test05@example.com</t>
-  </si>
-  <si>
-    <t>Test@202</t>
-  </si>
-  <si>
     <t>kavya.test06@example.com</t>
   </si>
   <si>
@@ -201,6 +186,9 @@
   </si>
   <si>
     <t>fail</t>
+  </si>
+  <si>
+    <t>summa</t>
   </si>
 </sst>
 </file>
@@ -270,10 +258,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{798466B8-8672-4CB5-9182-87D652BA1622}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.77734375" customWidth="1"/>
@@ -608,7 +592,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -619,144 +603,95 @@
         <v>123456</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>123456</v>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{B27F0493-28A0-4B75-9BA1-34F2A0E92947}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{33E3A2C8-4C8C-4457-871B-4394B17F6D75}"/>
-    <hyperlink ref="A4" r:id="rId3" display="mailto:sivakumar.test01@example.com" xr:uid="{4A1684AD-8B3F-4B9A-A920-97F8BA4A29AB}"/>
-    <hyperlink ref="A5" r:id="rId4" display="mailto:santhosh.test02@example.com" xr:uid="{511B95F0-F096-4225-B499-0AC9C8932CAB}"/>
-    <hyperlink ref="A7" r:id="rId5" display="mailto:arun.test04@example.com" xr:uid="{41A92B1A-A489-482C-8820-4873106ED8CB}"/>
-    <hyperlink ref="A8" r:id="rId6" display="mailto:priya.test05@example.com" xr:uid="{A76D7F7B-7589-4A88-9F71-90C697A63E13}"/>
-    <hyperlink ref="A9" r:id="rId7" display="mailto:kavya.test06@example.com" xr:uid="{66B8BDA5-BF58-4A11-82CC-B192E2B3B1D1}"/>
-    <hyperlink ref="A11" r:id="rId8" display="mailto:divya.test08@example.com" xr:uid="{AB5B4D43-AA83-4108-842B-FC1AD0CCA9B2}"/>
-    <hyperlink ref="A13" r:id="rId9" display="mailto:anitha.test10@example.com" xr:uid="{B872C053-BF0C-469D-ABFA-54EB2CC58BA5}"/>
-    <hyperlink ref="B13" r:id="rId10" xr:uid="{6C176E42-7FF6-4D39-A335-F43E9A74359C}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{2CF102D4-D426-43B2-B966-8FC7CC86D883}"/>
-    <hyperlink ref="B12" r:id="rId12" xr:uid="{01A16E32-5A28-423A-97BD-06559A8EC059}"/>
+    <hyperlink ref="A3" r:id="rId2" display="mailto:sivakumar.test01@example.com" xr:uid="{4A1684AD-8B3F-4B9A-A920-97F8BA4A29AB}"/>
+    <hyperlink ref="A5" r:id="rId3" display="mailto:arun.test04@example.com" xr:uid="{41A92B1A-A489-482C-8820-4873106ED8CB}"/>
+    <hyperlink ref="A6" r:id="rId4" display="mailto:kavya.test06@example.com" xr:uid="{66B8BDA5-BF58-4A11-82CC-B192E2B3B1D1}"/>
+    <hyperlink ref="A8" r:id="rId5" display="mailto:divya.test08@example.com" xr:uid="{AB5B4D43-AA83-4108-842B-FC1AD0CCA9B2}"/>
+    <hyperlink ref="A9" r:id="rId6" display="mailto:anitha.test10@example.com" xr:uid="{B872C053-BF0C-469D-ABFA-54EB2CC58BA5}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{6C176E42-7FF6-4D39-A335-F43E9A74359C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -775,7 +710,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -784,113 +719,113 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -923,28 +858,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
